--- a/src/data/exhibition-imports/2025-1-cupricina/maia_oprea.xlsx
+++ b/src/data/exhibition-imports/2025-1-cupricina/maia_oprea.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Study/Projects/Cutare/cutare-gallery/src/data/exhibition-imports/2025-1-cupricina/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C641DD7-0A07-464F-AD44-70F878B6D37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8396E691-C04A-204A-BD0B-D1DC72E9B9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <author>Eliza Balica</author>
   </authors>
   <commentList>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{D76744CC-DB04-8D40-B720-9432E2207477}">
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{D76744CC-DB04-8D40-B720-9432E2207477}">
       <text>
         <r>
           <rPr>
@@ -39,7 +39,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{EC8AFA6F-DF5D-BC40-BE74-A8E77B827617}">
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{EC8AFA6F-DF5D-BC40-BE74-A8E77B827617}">
       <text>
         <r>
           <rPr>
@@ -258,7 +258,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -293,6 +293,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -636,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="24" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.83203125" style="2" customWidth="1"/>
@@ -648,24 +651,18 @@
     <col min="7" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="9"/>
+    <row r="1" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>1</v>
@@ -674,10 +671,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>1</v>
@@ -686,74 +683,68 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="C5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="9"/>
+    </row>
     <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B9" s="6">
         <v>2025</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="6">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6">
         <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -900,16 +891,35 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B1:C1"/>
+  <mergeCells count="5">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{240F730C-D2A5-024D-ACD1-107BAECB8CC6}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{AD27DD45-C544-6649-AC4C-2782CC823838}"/>
+    <hyperlink ref="B4" r:id="rId1" xr:uid="{240F730C-D2A5-024D-ACD1-107BAECB8CC6}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{AD27DD45-C544-6649-AC4C-2782CC823838}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId3"/>
